--- a/data/trans_orig/P41C1_AOS_2023_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P41C1_AOS_2023_R-Habitat-trans_orig.xlsx
@@ -489,7 +489,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo medio en años que han tardado en que algún miembro de la pareja se quede embarazada</t>
+          <t>Tiempo medio en años que han tardado en que algún miembro de la pareja se quede embarazada (tasa de respuesta: 93,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -571,7 +571,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 9,92</t>
+          <t>1,3; 10,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -581,7 +581,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 8,34</t>
+          <t>1,79; 7,64</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 4,61</t>
+          <t>0,32; 4,61</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,48; 8,21</t>
+          <t>2,51; 7,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 6,56</t>
+          <t>2,08; 5,98</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,79; 5,0</t>
+          <t>1,4; 5,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 6,85</t>
+          <t>0,9; 6,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,8</t>
+          <t>1,75; 4,79</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,79</t>
+          <t>1,37; 2,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,95; 4,84</t>
+          <t>2,01; 4,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,6</t>
+          <t>1,87; 3,54</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,6</t>
+          <t>1,93; 4,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,56; 5,04</t>
+          <t>2,6; 5,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 4,31</t>
+          <t>2,47; 4,29</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41C1_AOS_2023_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P41C1_AOS_2023_R-Habitat-trans_orig.xlsx
@@ -548,17 +548,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>4,13</t>
+          <t>3,89</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4,08</t>
+          <t>4,07</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4,12</t>
+          <t>3,93</t>
         </is>
       </c>
     </row>
@@ -571,17 +571,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 10,45</t>
+          <t>1,28; 10,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,95</t>
+          <t>1,42; 5,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,79; 7,64</t>
+          <t>1,71; 8,11</t>
         </is>
       </c>
     </row>
@@ -598,17 +598,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2,23</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,44</t>
+          <t>4,02</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3,6</t>
+          <t>3,39</t>
         </is>
       </c>
     </row>
@@ -621,17 +621,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 4,61</t>
+          <t>0,26; 4,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,98</t>
+          <t>2,1; 7,38</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 5,98</t>
+          <t>1,99; 5,83</t>
         </is>
       </c>
     </row>
@@ -648,17 +648,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,55</t>
+          <t>3,8</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2,51</t>
+          <t>2,55</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,0</t>
+          <t>3,21</t>
         </is>
       </c>
     </row>
@@ -671,17 +671,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 5,0</t>
+          <t>2,2; 5,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 6,89</t>
+          <t>0,9; 7,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,79</t>
+          <t>1,86; 4,78</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>1,97</t>
+          <t>2,03</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2,54</t>
+          <t>2,56</t>
         </is>
       </c>
     </row>
@@ -721,17 +721,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 2,89</t>
+          <t>1,4; 2,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,51</t>
+          <t>2,05; 4,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,54</t>
+          <t>1,92; 3,65</t>
         </is>
       </c>
     </row>
@@ -748,17 +748,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,89</t>
+          <t>2,93</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,5</t>
+          <t>3,39</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3,2</t>
+          <t>3,17</t>
         </is>
       </c>
     </row>
@@ -771,17 +771,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,76</t>
+          <t>2,03; 4,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 5,07</t>
+          <t>2,41; 4,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,47; 4,29</t>
+          <t>2,5; 4,3</t>
         </is>
       </c>
     </row>
